--- a/InputMetadata/electrodes.xlsx
+++ b/InputMetadata/electrodes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikla\HiwiStuttgart\FictionalDatasetExample\InputMetadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikla\HiwiStuttgart\MUnitQuest_tutorials\InputMetadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D43615-B055-45AB-8C9E-CB27C51594B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC4C2F1-3E6C-4F72-A0F5-76AB0CC53583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{6E2ACFE9-4AC4-48A4-B903-324C8DBCA8DF}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="95">
   <si>
     <t>name</t>
   </si>
@@ -714,8 +714,7 @@
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="1.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -2778,10 +2777,13 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="D43">
+        <v>70</v>
       </c>
       <c r="E43" t="s">
         <v>91</v>
@@ -2825,10 +2827,13 @@
         <v>44</v>
       </c>
       <c r="B44">
+        <v>60</v>
+      </c>
+      <c r="C44">
         <v>50</v>
       </c>
-      <c r="C44">
-        <v>0</v>
+      <c r="D44">
+        <v>50</v>
       </c>
       <c r="E44" t="s">
         <v>91</v>
@@ -2872,10 +2877,13 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="D45">
+        <v>70</v>
       </c>
       <c r="E45" t="s">
         <v>91</v>
@@ -2919,10 +2927,13 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C46">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="D46">
+        <v>50</v>
       </c>
       <c r="E46" t="s">
         <v>91</v>
@@ -2966,13 +2977,13 @@
         <v>7</v>
       </c>
       <c r="B47">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47" t="s">
-        <v>5</v>
+        <v>50</v>
+      </c>
+      <c r="D47">
+        <v>100</v>
       </c>
       <c r="E47" t="s">
         <v>91</v>
@@ -3016,13 +3027,13 @@
         <v>9</v>
       </c>
       <c r="B48">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
+        <v>50</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
       </c>
       <c r="E48" t="s">
         <v>91</v>
@@ -3066,13 +3077,13 @@
         <v>74</v>
       </c>
       <c r="B49">
+        <v>100</v>
+      </c>
+      <c r="C49">
         <v>50</v>
       </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49" t="s">
-        <v>5</v>
+      <c r="D49">
+        <v>0</v>
       </c>
       <c r="E49" t="s">
         <v>91</v>
